--- a/Student Attendance/Class 2/Class 2 - Monthly Attendance - September-2024.xlsx
+++ b/Student Attendance/Class 2/Class 2 - Monthly Attendance - September-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\Class 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DADEC0-7430-43E4-BDFB-61CF9177D5A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932961D7-E8EE-489C-BD4B-C32CE7FB62DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="121">
   <si>
     <t>S.No</t>
   </si>
@@ -103,9 +103,6 @@
     <t>Year 2024</t>
   </si>
   <si>
-    <t>Monthly Attendence Month of August-2024</t>
-  </si>
-  <si>
     <t>Goverment High School (SJCHS)</t>
   </si>
   <si>
@@ -398,6 +395,9 @@
   </si>
   <si>
     <t>SUNDAY - SUNDAY - SUNDAY - SUNDAY - SUNDAY</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of September-2024</t>
   </si>
 </sst>
 </file>
@@ -671,6 +671,39 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -679,39 +712,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,46 +719,9 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -796,6 +759,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -844,14 +814,44 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1177,101 +1177,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
+      <c r="A1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
+      <c r="A2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1394,25 +1394,25 @@
         <f t="shared" si="1"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="32" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="29"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="21">
         <v>45536</v>
       </c>
@@ -1503,8 +1503,8 @@
       <c r="AI4" s="21">
         <v>45565</v>
       </c>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1520,104 +1520,106 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>120</v>
+      <c r="F5" s="22" t="s">
+        <v>119</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="33" t="s">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>119</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" s="33" t="s">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>119</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA5" s="33" t="s">
-        <v>120</v>
+        <v>35</v>
+      </c>
+      <c r="AA5" s="22" t="s">
+        <v>119</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH5" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI5" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="AH5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ5" s="5">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>17</v>
+        <f t="shared" ref="AJ5:AJ29" si="2">COUNTIF(F5:AI5,"P")</f>
+        <v>18</v>
       </c>
       <c r="AK5" s="5">
-        <f>COUNTIF(F5:AI5,"A")</f>
+        <f t="shared" ref="AK5:AK29" si="3">COUNTIF(F5:AI5,"A")</f>
         <v>5</v>
       </c>
       <c r="AL5" s="5" t="s">
@@ -1637,94 +1639,96 @@
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>59</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M6" s="23"/>
       <c r="N6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T6" s="23"/>
       <c r="U6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="11"/>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL6" s="5" t="s">
@@ -1742,94 +1746,96 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="34"/>
+      <c r="F7" s="23"/>
       <c r="G7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M7" s="23"/>
       <c r="N7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T7" s="23"/>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA7" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA7" s="23"/>
       <c r="AB7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH7" s="23"/>
+      <c r="AI7" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>22</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL7" s="3"/>
@@ -1843,102 +1849,104 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="34"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M8" s="23"/>
       <c r="N8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T8" s="23"/>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
       <c r="W8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA8" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA8" s="23"/>
       <c r="AB8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>19</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="AL8" s="27" t="s">
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="28"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="27"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1946,96 +1954,98 @@
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="34"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M9" s="23"/>
       <c r="N9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T9" s="23"/>
       <c r="U9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA9" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="AA9" s="23"/>
       <c r="AB9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>18</v>
+        <f t="shared" si="2"/>
+        <v>19</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AL9" s="5" t="s">
@@ -2057,94 +2067,96 @@
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="34"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M10" s="23"/>
       <c r="N10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T10" s="23"/>
       <c r="U10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA10" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA10" s="23"/>
       <c r="AB10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH10" s="23"/>
+      <c r="AI10" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>22</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL10" s="5" t="s">
@@ -2169,94 +2181,96 @@
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="34"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M11" s="23"/>
       <c r="N11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S11" s="11"/>
-      <c r="T11" s="34"/>
+      <c r="T11" s="23"/>
       <c r="U11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA11" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA11" s="23"/>
       <c r="AB11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH11" s="23"/>
+      <c r="AI11" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL11" s="5" t="s">
@@ -2264,15 +2278,15 @@
       </c>
       <c r="AM11" s="12">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28+AJ29</f>
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>485</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -2281,94 +2295,96 @@
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="34"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M12" s="23"/>
       <c r="N12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T12" s="23"/>
       <c r="U12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA12" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA12" s="23"/>
       <c r="AB12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH12" s="23"/>
+      <c r="AI12" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL12" s="5" t="s">
@@ -2376,15 +2392,15 @@
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>0.67611336032388669</v>
+        <v>0.708502024291498</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.27655677655677657</v>
+        <v>0.2893772893772894</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.46634615384615385</v>
+        <v>0.48846153846153845</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -2393,96 +2409,98 @@
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="34"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M13" s="23"/>
       <c r="N13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T13" s="34"/>
+        <v>54</v>
+      </c>
+      <c r="T13" s="23"/>
       <c r="U13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA13" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA13" s="23"/>
       <c r="AB13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AF13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH13" s="23"/>
+      <c r="AI13" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>18</v>
+        <f t="shared" si="2"/>
+        <v>19</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL13" s="3"/>
@@ -2496,94 +2514,96 @@
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="34"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M14" s="23"/>
       <c r="N14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T14" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T14" s="23"/>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
       <c r="W14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA14" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA14" s="23"/>
       <c r="AB14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF14" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL14" s="19"/>
@@ -2597,96 +2617,98 @@
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="34"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M15" s="23"/>
       <c r="N15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T15" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T15" s="23"/>
       <c r="U15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA15" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA15" s="23"/>
       <c r="AB15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH15" s="23"/>
+      <c r="AI15" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AL15" s="3"/>
@@ -2700,104 +2722,106 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="34"/>
+      <c r="F16" s="23"/>
       <c r="G16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M16" s="23"/>
       <c r="N16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T16" s="23"/>
       <c r="U16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="11"/>
       <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AL16" s="27" t="s">
+      <c r="AL16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="28"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="27"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2805,96 +2829,98 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="34"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M17" s="23"/>
       <c r="N17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T17" s="23"/>
       <c r="U17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA17" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA17" s="23"/>
       <c r="AB17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AF17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH17" s="23"/>
+      <c r="AI17" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AL17" s="5" t="s">
@@ -2916,96 +2942,98 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>69</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>70</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="34"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M18" s="23"/>
       <c r="N18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T18" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T18" s="23"/>
       <c r="U18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA18" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA18" s="23"/>
       <c r="AB18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH18" s="34"/>
-      <c r="AI18" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH18" s="23"/>
+      <c r="AI18" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL18" s="5" t="s">
@@ -3030,94 +3058,96 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="34"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M19" s="23"/>
       <c r="N19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T19" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T19" s="23"/>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
       <c r="W19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA19" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA19" s="23"/>
       <c r="AB19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH19" s="23"/>
+      <c r="AI19" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL19" s="5" t="s">
@@ -3125,15 +3155,15 @@
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>555</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -3142,96 +3172,98 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="34"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M20" s="23"/>
       <c r="N20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T20" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T20" s="23"/>
       <c r="U20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA20" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA20" s="23"/>
       <c r="AB20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH20" s="34"/>
-      <c r="AI20" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH20" s="23"/>
+      <c r="AI20" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL20" s="5" t="s">
@@ -3239,15 +3271,15 @@
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.32388663967611336</v>
+        <v>0.291497975708502</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.72344322344322343</v>
+        <v>0.71062271062271065</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.53365384615384615</v>
+        <v>0.5115384615384615</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -3256,96 +3288,98 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="34"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M21" s="23"/>
       <c r="N21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T21" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T21" s="23"/>
       <c r="U21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA21" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA21" s="23"/>
       <c r="AB21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH21" s="23"/>
+      <c r="AI21" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3355,96 +3389,98 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="34"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M22" s="23"/>
       <c r="N22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T22" s="23"/>
       <c r="U22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V22" s="11"/>
       <c r="W22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA22" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA22" s="23"/>
       <c r="AB22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH22" s="23"/>
+      <c r="AI22" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3454,94 +3490,96 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="34"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M23" s="23"/>
       <c r="N23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T23" s="23"/>
       <c r="U23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V23" s="11"/>
       <c r="W23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA23" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="AA23" s="23"/>
       <c r="AB23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC23" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD23" s="11"/>
       <c r="AE23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH23" s="23"/>
+      <c r="AI23" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>19</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -3551,96 +3589,98 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="34"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M24" s="23"/>
       <c r="N24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T24" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T24" s="23"/>
       <c r="U24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA24" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA24" s="23"/>
       <c r="AB24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH24" s="34"/>
-      <c r="AI24" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH24" s="23"/>
+      <c r="AI24" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -3650,96 +3690,98 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>78</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="34"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M25" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="M25" s="23"/>
       <c r="N25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T25" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T25" s="23"/>
       <c r="U25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V25" s="11"/>
       <c r="W25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA25" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="AA25" s="23"/>
       <c r="AB25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH25" s="34"/>
-      <c r="AI25" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH25" s="23"/>
+      <c r="AI25" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -3749,96 +3791,98 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>80</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="34"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M26" s="34"/>
+        <v>54</v>
+      </c>
+      <c r="M26" s="23"/>
       <c r="N26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T26" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T26" s="23"/>
       <c r="U26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V26" s="11"/>
       <c r="W26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA26" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA26" s="23"/>
       <c r="AB26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH26" s="34"/>
-      <c r="AI26" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH26" s="23"/>
+      <c r="AI26" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>22</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3848,70 +3892,72 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="34"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="34"/>
+      <c r="M27" s="23"/>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
       <c r="S27" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T27" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T27" s="23"/>
       <c r="U27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V27" s="11"/>
       <c r="W27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
       <c r="Z27" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA27" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA27" s="23"/>
       <c r="AB27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG27" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH27" s="34"/>
-      <c r="AI27" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH27" s="23"/>
+      <c r="AI27" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3921,70 +3967,72 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="34"/>
+      <c r="F28" s="23"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
-      <c r="M28" s="34"/>
+      <c r="M28" s="23"/>
       <c r="N28" s="11"/>
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T28" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="T28" s="23"/>
       <c r="U28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V28" s="11"/>
       <c r="W28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X28" s="11"/>
       <c r="Y28" s="11"/>
       <c r="Z28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA28" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="AA28" s="23"/>
       <c r="AB28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH28" s="34"/>
-      <c r="AI28" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH28" s="23"/>
+      <c r="AI28" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3994,134 +4042,136 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="35"/>
+      <c r="F29" s="24"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
-      <c r="M29" s="35"/>
+      <c r="M29" s="24"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
-      <c r="T29" s="35"/>
+      <c r="T29" s="24"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA29" s="35"/>
+        <v>36</v>
+      </c>
+      <c r="AA29" s="24"/>
       <c r="AB29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG29" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH29" s="35"/>
-      <c r="AI29" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH29" s="24"/>
+      <c r="AI29" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ29" s="5">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="AK29" s="5">
-        <f>COUNTIF(F29:AI29,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="F5:F29"/>
-    <mergeCell ref="M5:M29"/>
-    <mergeCell ref="T5:T29"/>
     <mergeCell ref="AA5:AA29"/>
     <mergeCell ref="AH5:AH29"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="F5:F29"/>
+    <mergeCell ref="M5:M29"/>
+    <mergeCell ref="T5:T29"/>
   </mergeCells>
-  <conditionalFormatting sqref="AL4:AM4 F3:AI4 G6:L29 N5:S29 F5:M5 U5:Z29 T5 AB5:AG29 AA5 AI5:AI29 AH5">
-    <cfRule type="expression" dxfId="16" priority="15">
+  <conditionalFormatting sqref="F5:M5 T5 AA5 AH5 N5:S29 U5:Z29 AB5:AG29 AI5:AI29 G6:L29 F4:AI4">
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:M5 T5 AA5 AH5 N5:S29 U5:Z29 AB5:AG29 AI5:AI29 G6:L29">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI4 F5:M5 T5 AA5 AH5 N5:S29 U5:Z29 AB5:AG29 AI5:AI29 G6:L29 AL4:AM4">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:AI4 G6:L29 N5:S29 F5:M5 U5:Z29 T5 AB5:AG29 AA5 AI5:AI29 AH5">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK29">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="11" priority="16">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="13" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>AM$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:L29 N5:S29 F5:M5 U5:Z29 T5 AB5:AG29 AA5 AI5:AI29 AH5">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4177,101 +4227,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
+      <c r="A1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
+      <c r="A2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -4394,25 +4444,25 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="32" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="29"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="21">
         <v>45536</v>
       </c>
@@ -4503,8 +4553,8 @@
       <c r="AI4" s="21">
         <v>45565</v>
       </c>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4520,107 +4570,109 @@
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>83</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>84</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>120</v>
+      <c r="F5" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" s="22" t="s">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH5" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI5" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH5" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="AJ5" s="5">
-        <f>COUNTIF(F5:AI5,"P")</f>
+        <f t="shared" ref="AJ5:AJ30" si="1">COUNTIF(F5:AI5,"P")</f>
         <v>23</v>
       </c>
       <c r="AK5" s="5">
-        <f>COUNTIF(F5:AI5,"A")</f>
-        <v>0</v>
+        <f t="shared" ref="AK5:AK30" si="2">COUNTIF(F5:AI5,"A")</f>
+        <v>1</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>8</v>
@@ -4639,96 +4691,98 @@
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M6" s="34"/>
       <c r="N6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T6" s="34"/>
       <c r="U6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA6" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA6" s="34"/>
       <c r="AB6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL6" s="5" t="s">
@@ -4746,94 +4800,96 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>85</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>86</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="M7" s="34"/>
       <c r="N7" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" s="11"/>
-      <c r="T7" s="23"/>
+      <c r="T7" s="34"/>
       <c r="U7" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA7" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD7" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH7" s="23"/>
-      <c r="AI7" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="AL7" s="3"/>
@@ -4847,104 +4903,106 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M8" s="34"/>
       <c r="N8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T8" s="34"/>
       <c r="U8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X8" s="11" t="s">
+      <c r="AE8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Y8" s="11" t="s">
+      <c r="AF8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Z8" s="11" t="s">
+      <c r="AG8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="11"/>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="27" t="s">
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="28"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="27"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
@@ -4952,94 +5010,96 @@
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>88</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M9" s="34"/>
       <c r="N9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T9" s="34"/>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA9" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA9" s="34"/>
       <c r="AB9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL9" s="5" t="s">
@@ -5061,96 +5121,98 @@
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>91</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M10" s="34"/>
       <c r="N10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T10" s="34"/>
       <c r="U10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X10" s="11" t="s">
+      <c r="AG10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Y10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="11"/>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL10" s="5" t="s">
@@ -5175,96 +5237,98 @@
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M11" s="34"/>
       <c r="N11" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="T11" s="34"/>
       <c r="U11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA11" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA11" s="34"/>
       <c r="AB11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE11" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AF11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH11" s="23"/>
-      <c r="AI11" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL11" s="5" t="s">
@@ -5272,15 +5336,15 @@
       </c>
       <c r="AM11" s="12">
         <f>AJ6+AJ17</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ7+AJ8+AJ9+AJ10+AJ11+AJ12+AJ13+AJ14+AJ15+AJ16+AJ18+AJ19</f>
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -5289,94 +5353,96 @@
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M12" s="34"/>
       <c r="N12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T12" s="34"/>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
       <c r="W12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA12" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA12" s="34"/>
       <c r="AB12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF12" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH12" s="23"/>
-      <c r="AI12" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL12" s="5" t="s">
@@ -5384,15 +5450,15 @@
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>7.8947368421052627E-2</v>
+        <v>8.2995951417004055E-2</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.45970695970695968</v>
+        <v>0.48168498168498169</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.27884615384615385</v>
+        <v>0.29230769230769232</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -5401,96 +5467,98 @@
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M13" s="34"/>
       <c r="N13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T13" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T13" s="34"/>
       <c r="U13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA13" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA13" s="34"/>
       <c r="AB13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH13" s="23"/>
-      <c r="AI13" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL13" s="3"/>
@@ -5504,96 +5572,98 @@
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="23"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M14" s="34"/>
       <c r="N14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T14" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T14" s="34"/>
       <c r="U14" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD14" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF14" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="11"/>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL14" s="19"/>
@@ -5607,96 +5677,98 @@
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="23"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M15" s="34"/>
       <c r="N15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T15" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T15" s="34"/>
       <c r="U15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA15" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA15" s="34"/>
       <c r="AB15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH15" s="23"/>
-      <c r="AI15" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL15" s="3"/>
@@ -5710,104 +5782,106 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="23"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M16" s="34"/>
       <c r="N16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T16" s="34"/>
       <c r="U16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA16" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA16" s="34"/>
       <c r="AB16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH16" s="23"/>
-      <c r="AI16" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AL16" s="27" t="s">
+      <c r="AL16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="28"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="27"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
@@ -5815,96 +5889,98 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>98</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>99</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="I17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M17" s="34"/>
       <c r="N17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T17" s="34"/>
       <c r="U17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA17" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA17" s="34"/>
       <c r="AB17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH17" s="23"/>
-      <c r="AI17" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL17" s="5" t="s">
@@ -5926,96 +6002,98 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M18" s="34"/>
       <c r="N18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T18" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T18" s="34"/>
       <c r="U18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA18" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA18" s="34"/>
       <c r="AB18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH18" s="23"/>
-      <c r="AI18" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL18" s="5" t="s">
@@ -6040,94 +6118,96 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>102</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M19" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="M19" s="34"/>
       <c r="N19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T19" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T19" s="34"/>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
       <c r="W19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA19" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA19" s="34"/>
       <c r="AB19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD19" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF19" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH19" s="23"/>
-      <c r="AI19" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="AL19" s="5" t="s">
@@ -6135,15 +6215,15 @@
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>750</v>
+        <v>736</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -6152,96 +6232,98 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="23"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M20" s="34"/>
       <c r="N20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T20" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T20" s="34"/>
       <c r="U20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA20" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA20" s="34"/>
       <c r="AB20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH20" s="23"/>
-      <c r="AI20" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL20" s="5" t="s">
@@ -6249,15 +6331,15 @@
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.92105263157894735</v>
+        <v>0.917004048582996</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.54029304029304026</v>
+        <v>0.51831501831501836</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.72115384615384615</v>
+        <v>0.70769230769230773</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -6266,94 +6348,96 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="23"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M21" s="34"/>
       <c r="N21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T21" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T21" s="34"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
       <c r="W21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG21" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH21" s="23"/>
-      <c r="AI21" s="11"/>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -6363,94 +6447,96 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M22" s="34"/>
       <c r="N22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T22" s="34"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA22" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA22" s="34"/>
       <c r="AB22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF22" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH22" s="23"/>
-      <c r="AI22" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -6460,94 +6546,96 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>107</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M23" s="34"/>
       <c r="N23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T23" s="34"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
       <c r="W23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA23" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA23" s="34"/>
       <c r="AB23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH23" s="23"/>
-      <c r="AI23" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -6557,96 +6645,98 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="23"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M24" s="34"/>
       <c r="N24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T24" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T24" s="34"/>
       <c r="U24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA24" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA24" s="34"/>
       <c r="AB24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH24" s="23"/>
-      <c r="AI24" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH24" s="34"/>
+      <c r="AI24" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6656,94 +6746,96 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>111</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M25" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M25" s="34"/>
       <c r="N25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P25" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T25" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="T25" s="34"/>
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
       <c r="W25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="X25" s="11" t="s">
+      <c r="AF25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Y25" s="11" t="s">
+      <c r="AG25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Z25" s="11" t="s">
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AA25" s="23"/>
-      <c r="AB25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH25" s="23"/>
-      <c r="AI25" s="11"/>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -6753,94 +6845,96 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="23"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M26" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M26" s="34"/>
       <c r="N26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O26" s="11"/>
       <c r="P26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T26" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="T26" s="34"/>
       <c r="U26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V26" s="11"/>
       <c r="W26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA26" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA26" s="34"/>
       <c r="AB26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH26" s="23"/>
-      <c r="AI26" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH26" s="34"/>
+      <c r="AI26" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -6850,96 +6944,98 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>113</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>114</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="23"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M27" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="M27" s="34"/>
       <c r="N27" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T27" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="T27" s="34"/>
       <c r="U27" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V27" s="11"/>
       <c r="W27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z27" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA27" s="23"/>
+        <v>35</v>
+      </c>
+      <c r="AA27" s="34"/>
       <c r="AB27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF27" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG27" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH27" s="23"/>
-      <c r="AI27" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -6949,96 +7045,98 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="23"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M28" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M28" s="34"/>
       <c r="N28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T28" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="T28" s="34"/>
       <c r="U28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V28" s="11"/>
       <c r="W28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA28" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="AA28" s="34"/>
       <c r="AB28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF28" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH28" s="23"/>
-      <c r="AI28" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH28" s="34"/>
+      <c r="AI28" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7048,92 +7146,94 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>116</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>117</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="23"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M29" s="23"/>
+        <v>36</v>
+      </c>
+      <c r="M29" s="34"/>
       <c r="N29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T29" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="T29" s="34"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z29" s="11"/>
-      <c r="AA29" s="23"/>
+      <c r="AA29" s="34"/>
       <c r="AB29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD29" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE29" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AF29" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG29" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH29" s="23"/>
-      <c r="AI29" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="AH29" s="34"/>
+      <c r="AI29" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ29" s="5">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="AK29" s="5">
-        <f>COUNTIF(F29:AI29,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -7143,101 +7243,110 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="16" t="s">
         <v>118</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>119</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="24"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M30" s="24"/>
+        <v>36</v>
+      </c>
+      <c r="M30" s="35"/>
       <c r="N30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T30" s="24"/>
+        <v>36</v>
+      </c>
+      <c r="T30" s="35"/>
       <c r="U30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V30" s="11"/>
       <c r="W30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA30" s="24"/>
+        <v>36</v>
+      </c>
+      <c r="AA30" s="35"/>
       <c r="AB30" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH30" s="24"/>
-      <c r="AI30" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="AH30" s="35"/>
+      <c r="AI30" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AJ30" s="5">
-        <f>COUNTIF(F30:AI30,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK30" s="5">
-        <f>COUNTIF(F30:AI30,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AM3"/>
@@ -7248,38 +7357,31 @@
     <mergeCell ref="T5:T30"/>
     <mergeCell ref="AA5:AA30"/>
     <mergeCell ref="AH5:AH30"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A2:AK2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:AI4 G6:L30 N5:S30 F5:M5 U5:Z30 T5 AB5:AG30 AA5 AI5:AI30 AH5 AL4:AM4 AL5:AL6 AL9:AL12 AL17:AL20 AM9:AO9 AM17:AO17">
-    <cfRule type="expression" dxfId="5" priority="10">
+  <conditionalFormatting sqref="F5:M5 T5 AA5 AH5 N5:S30 U5:Z30 AB5:AG30 AI5:AI30 G6:L30 F4:AI4">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:M5 T5 AA5 AH5 N5:S30 U5:Z30 AB5:AG30 AI5:AI30 G6:L30">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI4 F5:M5 T5 AA5 AH5 N5:S30 U5:Z30 AB5:AG30 AI5:AI30 G6:L30 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
+    <cfRule type="expression" dxfId="1" priority="10">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:AI4 G6:L30 N5:S30 F5:M5 U5:Z30 T5 AB5:AG30 AA5 AI5:AI30 AH5">
-    <cfRule type="expression" dxfId="4" priority="9">
-      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK30">
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>#REF!="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:L30 N5:S30 F5:M5 U5:Z30 T5 AB5:AG30 AA5 AI5:AI30 AH5">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
